--- a/Hypothesis_testing_results/Adults_tests_with_ICC_FORMULAS_Wilson.xlsx
+++ b/Hypothesis_testing_results/Adults_tests_with_ICC_FORMULAS_Wilson.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthi2revithiadou/Desktop/Lg&amp;Sp_reviews/article/revision/Suplemental_materials/Appendix_Hypothesis_testing_results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthi2revithiadou/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915FAF9C-C32F-FD48-A292-9657397D15DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2FACB14-7C2E-374D-A097-2372B187D424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3680" yWindow="2160" windowWidth="25720" windowHeight="14600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="660" windowWidth="24520" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t>Class</t>
   </si>
@@ -121,36 +121,6 @@
   </si>
   <si>
     <t>ICC_CI_high(Wilson)</t>
-  </si>
-  <si>
-    <t>p value</t>
-  </si>
-  <si>
-    <t>CI_low</t>
-  </si>
-  <si>
-    <t>Confidence Interval low</t>
-  </si>
-  <si>
-    <t>CI_high</t>
-  </si>
-  <si>
-    <t>Confidence Interval high</t>
-  </si>
-  <si>
-    <t>Significance level 0.05</t>
-  </si>
-  <si>
-    <t>ICC neff ρ</t>
-  </si>
-  <si>
-    <t>ICC Z score</t>
-  </si>
-  <si>
-    <t>ICC p value</t>
-  </si>
-  <si>
-    <t>ICC Significance level 0.05</t>
   </si>
 </sst>
 </file>
@@ -237,16 +207,28 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -581,7 +563,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="12.6640625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="5" customWidth="1"/>
     <col min="7" max="15" width="14.6640625" style="1" customWidth="1"/>
     <col min="16" max="16" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.5" bestFit="1" customWidth="1"/>
@@ -603,7 +586,7 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -653,10 +636,10 @@
       <c r="D2" s="1">
         <v>0.26984126984126983</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="1">
         <v>255</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="5">
         <v>945</v>
       </c>
       <c r="G2" s="1">
@@ -717,10 +700,10 @@
       <c r="D3" s="1">
         <v>0.71111111111111114</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="1">
         <v>672</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>945</v>
       </c>
       <c r="G3" s="1">
@@ -781,10 +764,10 @@
       <c r="D4" s="1">
         <v>0.14074074074074069</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="1">
         <v>133</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>945</v>
       </c>
       <c r="G4" s="1">
@@ -845,10 +828,10 @@
       <c r="D5" s="1">
         <v>0.76084656084656088</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="1">
         <v>719</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>945</v>
       </c>
       <c r="G5" s="1">
@@ -909,10 +892,10 @@
       <c r="D6" s="1">
         <v>8.4656084656084651E-2</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="1">
         <v>80</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>945</v>
       </c>
       <c r="G6" s="1">
@@ -973,10 +956,10 @@
       <c r="D7" s="1">
         <v>0.86031746031746037</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="1">
         <v>813</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>945</v>
       </c>
       <c r="G7" s="1">
@@ -1032,24 +1015,24 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>1.4999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="D8" s="1">
         <v>4.5502645502645503E-2</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="1">
         <v>43</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>945</v>
       </c>
       <c r="G8" s="1">
         <f>(D8-C8)/SQRT(C8*(1-C8)/F8)</f>
-        <v>7.7141781990622365</v>
+        <v>9.4585793363070287</v>
       </c>
       <c r="H8" s="1">
         <f>2*(1-_xlfn.NORM.S.DIST(ABS(G8),TRUE))</f>
-        <v>1.2212453270876722E-14</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1">
         <f>(D8 + 1.96^2/(2*F8) - 1.96*SQRT(D8*(1-D8)/F8 + 1.96^2/(4*F8^2)))/(1 + 1.96^2/F8)</f>
@@ -1069,11 +1052,11 @@
       </c>
       <c r="M8" s="1">
         <f>(D8-C8)/SQRT(C8*(1-C8)/L8)</f>
-        <v>4.7841302274727129</v>
+        <v>5.8659618878490685</v>
       </c>
       <c r="N8" s="1">
         <f>2*(1-_xlfn.NORM.S.DIST(ABS(M8),TRUE))</f>
-        <v>1.7172932209597036E-6</v>
+        <v>4.4653636344094139E-9</v>
       </c>
       <c r="O8" s="1" t="str">
         <f>IF(N8&lt;0.05,"Yes","No")</f>
@@ -1101,10 +1084,10 @@
       <c r="D9" s="1">
         <v>0.75449735449735444</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="1">
         <v>713</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="5">
         <v>945</v>
       </c>
       <c r="G9" s="1">
@@ -1166,10 +1149,10 @@
       <c r="D10" s="1">
         <v>0.89841269841269844</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="1">
         <v>849</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <v>945</v>
       </c>
       <c r="G10" s="1">
@@ -1231,10 +1214,10 @@
       <c r="D11" s="1">
         <v>9.5238095238095233E-2</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="1">
         <v>90</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="5">
         <v>945</v>
       </c>
       <c r="G11" s="1">
@@ -1295,10 +1278,10 @@
       <c r="D12" s="1">
         <v>0.60211640211640216</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="1">
         <v>569</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <v>945</v>
       </c>
       <c r="G12" s="1">
@@ -1359,10 +1342,10 @@
       <c r="D13" s="1">
         <v>0.33650793650793648</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="1">
         <v>318</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <v>945</v>
       </c>
       <c r="G13" s="1">
@@ -1423,10 +1406,10 @@
       <c r="D14" s="1">
         <v>0.48359788359788358</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="1">
         <v>457</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <v>945</v>
       </c>
       <c r="G14" s="1">
@@ -1487,10 +1470,10 @@
       <c r="D15" s="1">
         <v>0.36507936507936511</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="1">
         <v>345</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="5">
         <v>945</v>
       </c>
       <c r="G15" s="1">
@@ -1539,65 +1522,65 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
         <v>0.22589999999999999</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="7">
         <v>0.26984126984126983</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <v>255</v>
       </c>
       <c r="F16" s="8">
         <v>105</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="7">
         <f>(D16-C16)/SQRT(C16*(1-C16)/F16)</f>
         <v>1.0767393964986314</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="7">
         <f>2*(1-_xlfn.NORM.S.DIST(ABS(G16),TRUE))</f>
         <v>0.28159670667712389</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="7">
         <f>(D16 + 1.96^2/(2*F16) - 1.96*SQRT(D16*(1-D16)/F16 + 1.96^2/(4*F16^2)))/(1 + 1.96^2/F16)</f>
         <v>0.19417862411087586</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="7">
         <f>(D16 + 1.96^2/(2*F16) + 1.96*SQRT(D16*(1-D16)/F16 + 1.96^2/(4*F16^2)))/(1 + 1.96^2/F16)+1.96*SQRT(D16*(1-D16)/F16)</f>
         <v>0.44665420854018301</v>
       </c>
-      <c r="K16" s="6" t="str">
+      <c r="K16" s="7" t="str">
         <f>IF(H16&lt;0.05,"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="L16" s="6">
-        <f>(Params!$B$2*Params!$C$2)/(1+(Params!$C$2-1)*Params!$A$2)</f>
-        <v>363.46153846153845</v>
-      </c>
-      <c r="M16" s="6">
+      <c r="L16" s="7">
+        <f>(Params!$B$2*Params!$C$2)/(1+(Params!$C$2-1)*Params!$A$2)</f>
+        <v>363.46153846153845</v>
+      </c>
+      <c r="M16" s="7">
         <f>(D16-C16)/SQRT(C16*(1-C16)/L16)</f>
         <v>2.0032962789967836</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N16" s="7">
         <f>2*(1-_xlfn.NORM.S.DIST(ABS(M16),TRUE))</f>
         <v>4.5145496658696604E-2</v>
       </c>
-      <c r="O16" s="6" t="str">
+      <c r="O16" s="7" t="str">
         <f>IF(N16&lt;0.05,"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="P16" s="5">
+      <c r="P16" s="6">
         <f>(D16 + 1.96^2/(2*L16) - 1.96*SQRT(D16*(1-D16)/L16 + 1.96^2/(4*L16^2)))/(1 + 1.96^2/L16)</f>
         <v>0.22678985538190369</v>
       </c>
-      <c r="Q16" s="5">
+      <c r="Q16" s="6">
         <f>(D16 + 1.96^2/(2*L16) + 1.96*SQRT(D16*(1-D16)/L16 + 1.96^2/(4*L16^2)))/(1 + 1.96^2/L16)</f>
         <v>0.31770711513551092</v>
       </c>
@@ -1615,10 +1598,10 @@
       <c r="D17" s="1">
         <v>0.71111111111111114</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="1">
         <v>672</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="5">
         <v>105</v>
       </c>
       <c r="G17" s="1">
@@ -1679,10 +1662,10 @@
       <c r="D18" s="1">
         <v>0.14074074074074069</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="1">
         <v>133</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="5">
         <v>105</v>
       </c>
       <c r="G18" s="1">
@@ -1743,10 +1726,10 @@
       <c r="D19" s="1">
         <v>0.76084656084656088</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="1">
         <v>719</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="5">
         <v>105</v>
       </c>
       <c r="G19" s="1">
@@ -1807,10 +1790,10 @@
       <c r="D20" s="1">
         <v>8.4656084656084651E-2</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="1">
         <v>80</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="5">
         <v>105</v>
       </c>
       <c r="G20" s="1">
@@ -1871,10 +1854,10 @@
       <c r="D21" s="1">
         <v>0.86031746031746037</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="1">
         <v>813</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="5">
         <v>105</v>
       </c>
       <c r="G21" s="1">
@@ -1930,24 +1913,24 @@
         <v>13</v>
       </c>
       <c r="C22" s="1">
-        <v>1.4999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="D22" s="1">
         <v>4.5502645502645503E-2</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="1">
         <v>43</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="5">
         <v>105</v>
       </c>
       <c r="G22" s="1">
         <f>(D22-C22)/SQRT(C22*(1-C22)/F22)</f>
-        <v>2.5713927330207453</v>
+        <v>3.1528597787690096</v>
       </c>
       <c r="H22" s="1">
         <f>2*(1-_xlfn.NORM.S.DIST(ABS(G22),TRUE))</f>
-        <v>1.0129038831186765E-2</v>
+        <v>1.6167944948444202E-3</v>
       </c>
       <c r="I22" s="1">
         <f>(D22 + 1.96^2/(2*F22) - 1.96*SQRT(D22*(1-D22)/F22 + 1.96^2/(4*F22^2)))/(1 + 1.96^2/F22)</f>
@@ -1967,11 +1950,11 @@
       </c>
       <c r="M22" s="1">
         <f>(D22-C22)/SQRT(C22*(1-C22)/L22)</f>
-        <v>4.7841302274727129</v>
+        <v>5.8659618878490685</v>
       </c>
       <c r="N22" s="1">
         <f>2*(1-_xlfn.NORM.S.DIST(ABS(M22),TRUE))</f>
-        <v>1.7172932209597036E-6</v>
+        <v>4.4653636344094139E-9</v>
       </c>
       <c r="O22" s="1" t="str">
         <f>IF(N22&lt;0.05,"Yes","No")</f>
@@ -1999,10 +1982,10 @@
       <c r="D23" s="1">
         <v>0.75449735449735444</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="1">
         <v>713</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="5">
         <v>105</v>
       </c>
       <c r="G23" s="1">
@@ -2064,10 +2047,10 @@
       <c r="D24" s="1">
         <v>0.89841269841269844</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="1">
         <v>849</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="5">
         <v>105</v>
       </c>
       <c r="G24" s="1">
@@ -2129,10 +2112,10 @@
       <c r="D25" s="1">
         <v>9.5238095238095233E-2</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="1">
         <v>90</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="5">
         <v>105</v>
       </c>
       <c r="G25" s="1">
@@ -2193,10 +2176,10 @@
       <c r="D26" s="1">
         <v>0.60211640211640216</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="1">
         <v>569</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="5">
         <v>105</v>
       </c>
       <c r="G26" s="1">
@@ -2257,10 +2240,10 @@
       <c r="D27" s="1">
         <v>0.33650793650793648</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="1">
         <v>318</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="5">
         <v>105</v>
       </c>
       <c r="G27" s="1">
@@ -2321,10 +2304,10 @@
       <c r="D28" s="1">
         <v>0.48359788359788358</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="1">
         <v>457</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="5">
         <v>105</v>
       </c>
       <c r="G28" s="1">
@@ -2385,10 +2368,10 @@
       <c r="D29" s="1">
         <v>0.36507936507936511</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="1">
         <v>345</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="5">
         <v>105</v>
       </c>
       <c r="G29" s="1">
@@ -2438,15 +2421,20 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q29">
-    <sortCondition descending="1" ref="F1:F29"/>
+    <sortCondition descending="1" ref="F7:F29"/>
   </sortState>
   <conditionalFormatting sqref="K2:K29">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O29">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2461,7 +2449,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.1640625" customWidth="1"/>
@@ -2490,70 +2478,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
